--- a/media/contacts/murojaatlar.xlsx
+++ b/media/contacts/murojaatlar.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 11:55</t>
+          <t>2026-10-26 12:05</t>
         </is>
       </c>
     </row>

--- a/media/contacts/murojaatlar.xlsx
+++ b/media/contacts/murojaatlar.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 12:05</t>
+          <t>2026-10-26 14:15</t>
         </is>
       </c>
     </row>
